--- a/output/results_test.xlsx
+++ b/output/results_test.xlsx
@@ -2,12 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="follow_up_status" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Neuro_Deficit_Type" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,25 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
@@ -49,29 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -87,43 +54,16 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -202,10 +142,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -243,71 +183,69 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -331,53 +269,54 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
                 <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="51000"/>
+                <a:shade val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
+                <a:shade val="93000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="94000"/>
+                <a:shade val="94000"/>
                 <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
-              <a:shade val="9500"/>
+              <a:shade val="95000"/>
               <a:satMod val="105000"/>
             </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -387,7 +326,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -396,7 +335,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -405,7 +344,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -413,10 +352,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -445,7 +384,7 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="20000"/>
+                <a:shade val="20000"/>
                 <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
@@ -458,12 +397,13 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
                 <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
+                <a:shade val="30000"/>
                 <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
@@ -483,13 +423,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -499,53 +439,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filename</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
-        <is>
-          <t>follow_up_status</t>
-        </is>
-      </c>
-      <c r="D1" s="10" t="inlineStr">
-        <is>
-          <t>follow_up_imaging_type</t>
-        </is>
-      </c>
-      <c r="E1" s="10" t="inlineStr">
-        <is>
-          <t>patient_status_from_follow_up_imaging</t>
-        </is>
-      </c>
-      <c r="F1" s="10" t="inlineStr">
-        <is>
-          <t>answer_facts</t>
-        </is>
-      </c>
-      <c r="G1" s="10" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>neurologic_deficit_type</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>chain_of_thought</t>
-        </is>
-      </c>
-      <c r="H1" s="10" t="inlineStr">
-        <is>
-          <t>answer_consistency</t>
-        </is>
-      </c>
-      <c r="I1" s="10" t="inlineStr">
-        <is>
-          <t>all_answers</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="n">
+      <c r="A2" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -555,32 +470,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>[{'fact': 'She was scheduled to have a MRI to re-evaluate the CVST and determine if Xarelto will need to be continued, but the MRI has been postponed to an undetermined date.', 'substring_quote': ['She was scheduled to have a MRI to re-evaluate the CVST and determine if Xarelto will need to be continued, but the MRI has been postponed to an undetermined date.']}, {'fact': "She has responded well to eliquis, but now needs repeat MRV to evaluate thrombus burden. She hasn't gone as previously scheduled.", 'substring_quote': ["She hasn't gone as previously scheduled."]}, {'fact': 'Schedule MRI/MRV to see changes since last imaging.', 'substring_quote': ['Schedule MRI/MRV to see changes since last imaging.']}]</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>The patient was scheduled for a follow-up MRI to re-evaluate the CVST, but it has been postponed to an undetermined date. Additionally, it is mentioned that she needs a repeat MRV to evaluate thrombus burden, but she hasn't gone as previously scheduled. Therefore, it is clear that the patient has not had a follow-up brain imaging since discharge or their last visit.</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>['No', 'No', 'No']</t>
+          <t>['Speech']</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>The clinical note mentions that the patient is currently speaking with 3 word phrases that are sometimes understandable and occasionally says 2 word phrases during the encounter. This indicates a speech deficit.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="n">
+      <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,35 +490,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>['Cognitive', 'Speech', 'Motor']</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>['CT', 'MRI', 'MRA']</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Stable</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>[{'fact': 'In the ED, a CTH was done and ruled out an intracranial abnormality.', 'substring_quote': ['CTH was done']}, {'fact': 'An MRI of the orbits was done and showed no acute changes.', 'substring_quote': ['MRI of the orbits was done']}, {'fact': 'MRI/MRA: Extensive left hemispheric predominantly cortical parenchymal injury and volume loss, likely related to history of meningitis and associated left MCA territory stroke related to vasculitis.', 'substring_quote': []}, {'fact': 'Diffuse mild asymmetric decrease in caliber of the left middle cerebral artery and branch vessels compared to the right, also likely related to history of meningitis and associated left MCA territory vasculitis.', 'substring_quote': ['Diffuse mild asymmetric decrease in caliber of the left middle cerebral artery and branch vessels compared to the right']}]</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>The patient had multiple follow-up brain imaging studies since discharge. A CT head (CTH) was done in the ED, and an MRI of the orbits was performed, both of which are follow-up imaging types. Additionally, an MRI/MRA was conducted, showing extensive left hemispheric injury and volume loss, and a decrease in the caliber of the left middle cerebral artery. These imaging results indicate that the patient had follow-up imaging, and the findings were consistent with her known history, suggesting a stable condition.</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>['Yes', 'Yes', 'Yes']</t>
+          <t>The clinical note mentions several neurological deficits directly. The patient has 'decreased recent memory' and 'attention span/concentration decreased for age,' which are cognitive deficits. The note also states 'some word-finding difficulties and problems with fluency in English,' indicating a speech deficit. Additionally, the patient has 'decreased bulk' and specific strength deficits in the right upper and lower extremities, which are motor deficits.</t>
         </is>
       </c>
     </row>
